--- a/tests/MDI-To-EDRS.xlsx
+++ b/tests/MDI-To-EDRS.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mc142/Documents/workspace/mortality-reporting/mdi-import/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43ED1451-B0D2-6349-8D47-5B3BB1A4B266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5F46C3-D5E7-C74C-8FD8-932FD457A13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34560" windowHeight="20560" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20560" xr2:uid="{7A50F290-1C75-487E-9806-F93553E4E7CC}"/>
   </bookViews>
   <sheets>
-    <sheet name="MDI RAVEN Input Schema" sheetId="4" r:id="rId1"/>
+    <sheet name="MDI and EDRS" sheetId="4" r:id="rId1"/>
     <sheet name="Drop Down List Values" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="281">
   <si>
     <t>Sections</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t>End of Cases</t>
-  </si>
-  <si>
-    <t>This Excel File can be imported into RAVEN2.0; converting into FHIR and importing into RAVEN</t>
   </si>
   <si>
     <t>File Id</t>
@@ -970,6 +967,15 @@
   </si>
   <si>
     <t>Chicago</t>
+  </si>
+  <si>
+    <t>Usecase</t>
+  </si>
+  <si>
+    <t>MDI and EDRS FHIR Profile</t>
+  </si>
+  <si>
+    <t>This Excel File can be imported into RAVEN. Mapping data in this file to MDI and EDRS FHIR Profile</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1276,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -1690,6 +1696,9 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2064,28 +2073,34 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="49" t="s">
+        <v>278</v>
+      </c>
+      <c r="B2" s="132" t="s">
+        <v>279</v>
+      </c>
       <c r="C2" s="68" t="s">
-        <v>9</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="105.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="107" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" s="100" t="s">
         <v>10</v>
-      </c>
-      <c r="B3" s="107" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" s="100" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="4" customFormat="1" ht="40" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" s="50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="62"/>
       <c r="C4" s="81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -2097,22 +2112,22 @@
     <row r="5" spans="1:9" s="6" customFormat="1" ht="31" x14ac:dyDescent="0.3">
       <c r="A5" s="51"/>
       <c r="B5" s="97" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="82" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="48" t="s">
         <v>179</v>
       </c>
-      <c r="E5" s="48" t="s">
+      <c r="F5" s="48" t="s">
         <v>180</v>
       </c>
-      <c r="F5" s="48" t="s">
+      <c r="G5" s="48" t="s">
         <v>181</v>
-      </c>
-      <c r="G5" s="48" t="s">
-        <v>182</v>
       </c>
       <c r="H5" s="48"/>
       <c r="I5" s="5"/>
@@ -2120,33 +2135,33 @@
     <row r="6" spans="1:9" s="6" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A6" s="51"/>
       <c r="B6" s="98" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="82" t="s">
-        <v>17</v>
-      </c>
       <c r="D6" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="E6" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="F6" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="G6" s="48" t="s">
         <v>185</v>
-      </c>
-      <c r="G6" s="48" t="s">
-        <v>186</v>
       </c>
       <c r="H6" s="48"/>
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" s="8" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A7" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="63"/>
       <c r="C7" s="83" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -2158,22 +2173,22 @@
     <row r="8" spans="1:9" s="11" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A8" s="53"/>
       <c r="B8" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="84" t="s">
-        <v>21</v>
-      </c>
       <c r="D8" s="109" t="s">
+        <v>186</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>189</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>190</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="10"/>
@@ -2181,22 +2196,22 @@
     <row r="9" spans="1:9" s="11" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A9" s="53"/>
       <c r="B9" s="69" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="84" t="s">
+      <c r="D9" s="109" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="109" t="s">
-        <v>138</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>24</v>
-      </c>
       <c r="F9" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="10"/>
@@ -2204,22 +2219,22 @@
     <row r="10" spans="1:9" s="11" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="53"/>
       <c r="B10" s="69" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="84" t="s">
+      <c r="D10" s="109" t="s">
+        <v>190</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="109" t="s">
-        <v>191</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>27</v>
-      </c>
       <c r="F10" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="10"/>
@@ -2227,22 +2242,22 @@
     <row r="11" spans="1:9" s="11" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A11" s="53"/>
       <c r="B11" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="84" t="s">
+      <c r="D11" s="109" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="109" t="s">
-        <v>30</v>
-      </c>
       <c r="E11" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="10"/>
@@ -2250,16 +2265,16 @@
     <row r="12" spans="1:9" s="11" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A12" s="53"/>
       <c r="B12" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="84" t="s">
         <v>31</v>
-      </c>
-      <c r="C12" s="84" t="s">
-        <v>32</v>
       </c>
       <c r="D12" s="109">
         <v>472895623</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F12" s="9">
         <v>472962356</v>
@@ -2273,13 +2288,13 @@
     <row r="13" spans="1:9" s="11" customFormat="1" ht="65" x14ac:dyDescent="0.3">
       <c r="A13" s="53"/>
       <c r="B13" s="69" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="84" t="s">
-        <v>34</v>
-      </c>
       <c r="D13" s="109" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E13" s="9">
         <v>23</v>
@@ -2296,10 +2311,10 @@
     <row r="14" spans="1:9" s="11" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A14" s="53"/>
       <c r="B14" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="84" t="s">
         <v>35</v>
-      </c>
-      <c r="C14" s="84" t="s">
-        <v>36</v>
       </c>
       <c r="D14" s="110">
         <v>25225</v>
@@ -2319,20 +2334,20 @@
     <row r="15" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="53"/>
       <c r="B15" s="69" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" s="84"/>
       <c r="D15" s="109" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E15" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="10"/>
@@ -2340,22 +2355,22 @@
     <row r="16" spans="1:9" s="11" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A16" s="53"/>
       <c r="B16" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="84" t="s">
-        <v>39</v>
-      </c>
       <c r="D16" s="121" t="s">
+        <v>196</v>
+      </c>
+      <c r="E16" s="122" t="s">
         <v>197</v>
       </c>
-      <c r="E16" s="122" t="s">
+      <c r="F16" s="122" t="s">
         <v>198</v>
       </c>
-      <c r="F16" s="122" t="s">
+      <c r="G16" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>200</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="10"/>
@@ -2363,20 +2378,20 @@
     <row r="17" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="53"/>
       <c r="B17" s="69" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C17" s="84"/>
       <c r="D17" s="109" t="s">
+        <v>200</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="G17" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="10"/>
@@ -2384,20 +2399,20 @@
     <row r="18" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="53"/>
       <c r="B18" s="69" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18" s="84"/>
       <c r="D18" s="109" t="s">
+        <v>204</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="F18" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="G18" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="H18" s="9"/>
       <c r="I18" s="10"/>
@@ -2405,20 +2420,20 @@
     <row r="19" spans="1:9" s="11" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A19" s="53"/>
       <c r="B19" s="71" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="84"/>
       <c r="D19" s="109" t="s">
+        <v>207</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="F19" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="G19" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="10"/>
@@ -2426,7 +2441,7 @@
     <row r="20" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="53"/>
       <c r="B20" s="69" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" s="84"/>
       <c r="D20" s="109">
@@ -2447,31 +2462,31 @@
     <row r="21" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="53"/>
       <c r="B21" s="69" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="84"/>
       <c r="D21" s="109" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="10"/>
     </row>
     <row r="22" spans="1:9" s="14" customFormat="1" ht="91" x14ac:dyDescent="0.3">
       <c r="A22" s="94" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="64"/>
       <c r="C22" s="85" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
@@ -2483,22 +2498,22 @@
     <row r="23" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="54"/>
       <c r="B23" s="99" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="86" t="s">
-        <v>46</v>
-      </c>
       <c r="D23" s="116" t="s">
+        <v>210</v>
+      </c>
+      <c r="E23" s="117" t="s">
         <v>211</v>
       </c>
-      <c r="E23" s="117" t="s">
+      <c r="F23" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="F23" s="117" t="s">
+      <c r="G23" s="117" t="s">
         <v>213</v>
-      </c>
-      <c r="G23" s="117" t="s">
-        <v>214</v>
       </c>
       <c r="H23" s="15"/>
       <c r="I23" s="16"/>
@@ -2506,19 +2521,19 @@
     <row r="24" spans="1:9" s="17" customFormat="1" ht="32" x14ac:dyDescent="0.3">
       <c r="A24" s="54"/>
       <c r="B24" s="99" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="86" t="s">
-        <v>48</v>
-      </c>
       <c r="D24" s="112" t="s">
+        <v>214</v>
+      </c>
+      <c r="E24" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="F24" s="118" t="s">
         <v>216</v>
-      </c>
-      <c r="F24" s="118" t="s">
-        <v>217</v>
       </c>
       <c r="G24" s="18"/>
       <c r="H24" s="18"/>
@@ -2527,14 +2542,14 @@
     <row r="25" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="54"/>
       <c r="B25" s="99" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="86" t="s">
         <v>49</v>
-      </c>
-      <c r="C25" s="86" t="s">
-        <v>50</v>
       </c>
       <c r="D25" s="113"/>
       <c r="E25" s="19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F25" s="19"/>
       <c r="G25" s="19"/>
@@ -2544,10 +2559,10 @@
     <row r="26" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="54"/>
       <c r="B26" s="99" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="86" t="s">
         <v>51</v>
-      </c>
-      <c r="C26" s="86" t="s">
-        <v>52</v>
       </c>
       <c r="D26" s="113"/>
       <c r="E26" s="19"/>
@@ -2559,16 +2574,16 @@
     <row r="27" spans="1:9" s="17" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A27" s="54"/>
       <c r="B27" s="99" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="86" t="s">
-        <v>54</v>
-      </c>
       <c r="D27" s="113" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F27" s="19"/>
       <c r="G27" s="19"/>
@@ -2578,16 +2593,16 @@
     <row r="28" spans="1:9" s="17" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A28" s="54"/>
       <c r="B28" s="99" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="86" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="86" t="s">
-        <v>56</v>
-      </c>
       <c r="D28" s="113" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F28" s="19"/>
       <c r="G28" s="19"/>
@@ -2597,14 +2612,14 @@
     <row r="29" spans="1:9" s="17" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A29" s="54"/>
       <c r="B29" s="99" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="86" t="s">
         <v>57</v>
-      </c>
-      <c r="C29" s="86" t="s">
-        <v>58</v>
       </c>
       <c r="D29" s="113"/>
       <c r="E29" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F29" s="19"/>
       <c r="G29" s="19"/>
@@ -2614,10 +2629,10 @@
     <row r="30" spans="1:9" s="17" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A30" s="54"/>
       <c r="B30" s="99" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="86" t="s">
         <v>59</v>
-      </c>
-      <c r="C30" s="86" t="s">
-        <v>60</v>
       </c>
       <c r="D30" s="111"/>
       <c r="E30" s="15"/>
@@ -2629,19 +2644,19 @@
     <row r="31" spans="1:9" s="17" customFormat="1" ht="48" x14ac:dyDescent="0.3">
       <c r="A31" s="54"/>
       <c r="B31" s="99" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="86" t="s">
-        <v>62</v>
-      </c>
       <c r="D31" s="113" t="s">
+        <v>220</v>
+      </c>
+      <c r="E31" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="F31" s="20" t="s">
         <v>222</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>223</v>
       </c>
       <c r="G31" s="20"/>
       <c r="H31" s="20"/>
@@ -2650,22 +2665,22 @@
     <row r="32" spans="1:9" s="17" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A32" s="54"/>
       <c r="B32" s="72" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="86" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="86" t="s">
+      <c r="D32" s="114" t="s">
         <v>64</v>
       </c>
-      <c r="D32" s="114" t="s">
-        <v>65</v>
-      </c>
       <c r="E32" s="20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H32" s="20"/>
       <c r="I32" s="16"/>
@@ -2673,10 +2688,10 @@
     <row r="33" spans="1:9" s="17" customFormat="1" ht="65" x14ac:dyDescent="0.3">
       <c r="A33" s="54"/>
       <c r="B33" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="86" t="s">
         <v>66</v>
-      </c>
-      <c r="C33" s="86" t="s">
-        <v>67</v>
       </c>
       <c r="D33" s="115">
         <v>44460</v>
@@ -2694,10 +2709,10 @@
     <row r="34" spans="1:9" s="17" customFormat="1" ht="91" x14ac:dyDescent="0.3">
       <c r="A34" s="54"/>
       <c r="B34" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="86" t="s">
         <v>68</v>
-      </c>
-      <c r="C34" s="86" t="s">
-        <v>69</v>
       </c>
       <c r="D34" s="119">
         <v>0.93125000000000002</v>
@@ -2715,20 +2730,20 @@
     <row r="35" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="55"/>
       <c r="B35" s="72" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="86" t="s">
-        <v>71</v>
-      </c>
       <c r="D35" s="113" t="s">
+        <v>223</v>
+      </c>
+      <c r="E35" s="19" t="s">
         <v>224</v>
-      </c>
-      <c r="E35" s="19" t="s">
-        <v>225</v>
       </c>
       <c r="F35" s="19"/>
       <c r="G35" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H35" s="19"/>
       <c r="I35" s="23"/>
@@ -2736,22 +2751,22 @@
     <row r="36" spans="1:9" s="17" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A36" s="54"/>
       <c r="B36" s="72" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="86" t="s">
+      <c r="D36" s="114" t="s">
         <v>73</v>
       </c>
-      <c r="D36" s="114" t="s">
-        <v>74</v>
-      </c>
       <c r="E36" s="20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H36" s="20"/>
       <c r="I36" s="16"/>
@@ -2759,13 +2774,13 @@
     <row r="37" spans="1:9" s="17" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A37" s="54"/>
       <c r="B37" s="72" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="86" t="s">
-        <v>76</v>
-      </c>
       <c r="D37" s="114" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E37" s="20"/>
       <c r="F37" s="20"/>
@@ -2775,11 +2790,11 @@
     </row>
     <row r="38" spans="1:9" s="26" customFormat="1" ht="91" x14ac:dyDescent="0.3">
       <c r="A38" s="95" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B38" s="65"/>
       <c r="C38" s="87" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D38" s="25"/>
       <c r="E38" s="25"/>
@@ -2791,20 +2806,20 @@
     <row r="39" spans="1:9" s="29" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A39" s="56"/>
       <c r="B39" s="73" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C39" s="88" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D39" s="79" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F39" s="27"/>
       <c r="G39" s="27" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H39" s="27"/>
       <c r="I39" s="28"/>
@@ -2812,15 +2827,15 @@
     <row r="40" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="56"/>
       <c r="B40" s="73" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C40" s="88"/>
       <c r="D40" s="79" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E40" s="27"/>
       <c r="F40" s="27" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G40" s="27"/>
       <c r="H40" s="27"/>
@@ -2829,13 +2844,13 @@
     <row r="41" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="56"/>
       <c r="B41" s="73" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C41" s="88"/>
       <c r="D41" s="79"/>
       <c r="E41" s="27"/>
       <c r="F41" s="27" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G41" s="27"/>
       <c r="H41" s="27"/>
@@ -2844,11 +2859,11 @@
     <row r="42" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="56"/>
       <c r="B42" s="73" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C42" s="88"/>
       <c r="D42" s="79" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E42" s="27"/>
       <c r="F42" s="27"/>
@@ -2859,7 +2874,7 @@
     <row r="43" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="56"/>
       <c r="B43" s="73" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="88"/>
       <c r="D43" s="79">
@@ -2874,7 +2889,7 @@
     <row r="44" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="56"/>
       <c r="B44" s="73" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C44" s="88"/>
       <c r="D44" s="79"/>
@@ -2887,16 +2902,16 @@
     <row r="45" spans="1:9" s="29" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A45" s="56"/>
       <c r="B45" s="74" t="s">
+        <v>252</v>
+      </c>
+      <c r="C45" s="88" t="s">
         <v>253</v>
       </c>
-      <c r="C45" s="88" t="s">
-        <v>254</v>
-      </c>
       <c r="D45" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="E45" s="128" t="s">
         <v>260</v>
-      </c>
-      <c r="E45" s="128" t="s">
-        <v>261</v>
       </c>
       <c r="F45" s="27"/>
       <c r="G45" s="128"/>
@@ -2906,20 +2921,20 @@
     <row r="46" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="56"/>
       <c r="B46" s="74" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C46" s="88"/>
       <c r="D46" s="79" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E46" s="128" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F46" s="27" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G46" s="128" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H46" s="128"/>
       <c r="I46" s="28"/>
@@ -2927,13 +2942,13 @@
     <row r="47" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="56"/>
       <c r="B47" s="74" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C47" s="88"/>
       <c r="D47" s="79"/>
       <c r="E47" s="128"/>
       <c r="F47" s="27" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G47" s="128"/>
       <c r="H47" s="128"/>
@@ -2942,20 +2957,20 @@
     <row r="48" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="56"/>
       <c r="B48" s="74" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C48" s="88"/>
       <c r="D48" s="79" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E48" s="128" t="s">
+        <v>262</v>
+      </c>
+      <c r="F48" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="F48" s="27" t="s">
-        <v>264</v>
-      </c>
       <c r="G48" s="128" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H48" s="128"/>
       <c r="I48" s="28"/>
@@ -2963,7 +2978,7 @@
     <row r="49" spans="1:47" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="56"/>
       <c r="B49" s="74" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C49" s="88"/>
       <c r="D49" s="79">
@@ -2984,7 +2999,7 @@
     <row r="50" spans="1:47" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="56"/>
       <c r="B50" s="74" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C50" s="88"/>
       <c r="D50" s="79"/>
@@ -2997,22 +3012,22 @@
     <row r="51" spans="1:47" s="29" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A51" s="56"/>
       <c r="B51" s="73" t="s">
+        <v>78</v>
+      </c>
+      <c r="C51" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="C51" s="88" t="s">
+      <c r="D51" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="79" t="s">
-        <v>81</v>
-      </c>
       <c r="E51" s="79" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F51" s="79" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G51" s="79" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H51" s="79"/>
       <c r="I51" s="28"/>
@@ -3020,33 +3035,33 @@
     <row r="52" spans="1:47" s="29" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A52" s="56"/>
       <c r="B52" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" s="88" t="s">
         <v>82</v>
       </c>
-      <c r="C52" s="88" t="s">
-        <v>83</v>
-      </c>
       <c r="D52" s="79" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E52" s="27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F52" s="27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G52" s="27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H52" s="27"/>
       <c r="I52" s="28"/>
     </row>
     <row r="53" spans="1:47" s="32" customFormat="1" ht="65" x14ac:dyDescent="0.3">
       <c r="A53" s="101" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B53" s="66"/>
       <c r="C53" s="89" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D53" s="123"/>
       <c r="E53" s="30"/>
@@ -3058,22 +3073,22 @@
     <row r="54" spans="1:47" s="35" customFormat="1" ht="52" x14ac:dyDescent="0.3">
       <c r="A54" s="57"/>
       <c r="B54" s="75" t="s">
+        <v>85</v>
+      </c>
+      <c r="C54" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="C54" s="90" t="s">
-        <v>87</v>
-      </c>
       <c r="D54" s="124" t="s">
+        <v>227</v>
+      </c>
+      <c r="E54" s="33" t="s">
         <v>228</v>
       </c>
-      <c r="E54" s="33" t="s">
+      <c r="F54" s="33" t="s">
         <v>229</v>
       </c>
-      <c r="F54" s="33" t="s">
+      <c r="G54" s="33" t="s">
         <v>230</v>
-      </c>
-      <c r="G54" s="33" t="s">
-        <v>231</v>
       </c>
       <c r="H54" s="33"/>
       <c r="I54" s="34"/>
@@ -3081,22 +3096,22 @@
     <row r="55" spans="1:47" s="35" customFormat="1" ht="91" x14ac:dyDescent="0.3">
       <c r="A55" s="57"/>
       <c r="B55" s="75" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" s="90" t="s">
         <v>88</v>
       </c>
-      <c r="C55" s="90" t="s">
-        <v>89</v>
-      </c>
       <c r="D55" s="125" t="s">
+        <v>231</v>
+      </c>
+      <c r="E55" s="36" t="s">
         <v>232</v>
       </c>
-      <c r="E55" s="36" t="s">
+      <c r="F55" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="F55" s="36" t="s">
+      <c r="G55" s="36" t="s">
         <v>234</v>
-      </c>
-      <c r="G55" s="36" t="s">
-        <v>235</v>
       </c>
       <c r="H55" s="36"/>
       <c r="I55" s="34"/>
@@ -3104,13 +3119,13 @@
     <row r="56" spans="1:47" s="35" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A56" s="57"/>
       <c r="B56" s="75" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="C56" s="90" t="s">
+      <c r="D56" s="126" t="s">
         <v>91</v>
-      </c>
-      <c r="D56" s="126" t="s">
-        <v>92</v>
       </c>
       <c r="E56" s="37"/>
       <c r="F56" s="37"/>
@@ -3121,10 +3136,10 @@
     <row r="57" spans="1:47" s="35" customFormat="1" ht="65" x14ac:dyDescent="0.3">
       <c r="A57" s="57"/>
       <c r="B57" s="75" t="s">
+        <v>92</v>
+      </c>
+      <c r="C57" s="90" t="s">
         <v>93</v>
-      </c>
-      <c r="C57" s="90" t="s">
-        <v>94</v>
       </c>
       <c r="D57" s="127">
         <v>44462</v>
@@ -3144,22 +3159,22 @@
     <row r="58" spans="1:47" s="35" customFormat="1" ht="91" x14ac:dyDescent="0.3">
       <c r="A58" s="57"/>
       <c r="B58" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="C58" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="C58" s="90" t="s">
-        <v>96</v>
-      </c>
       <c r="D58" s="125" t="s">
+        <v>235</v>
+      </c>
+      <c r="E58" s="36" t="s">
         <v>236</v>
       </c>
-      <c r="E58" s="36" t="s">
-        <v>237</v>
-      </c>
       <c r="F58" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="G58" s="36" t="s">
         <v>234</v>
-      </c>
-      <c r="G58" s="36" t="s">
-        <v>235</v>
       </c>
       <c r="H58" s="36"/>
       <c r="I58" s="34"/>
@@ -3167,33 +3182,33 @@
     <row r="59" spans="1:47" s="35" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A59" s="57"/>
       <c r="B59" s="75" t="s">
+        <v>96</v>
+      </c>
+      <c r="C59" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="C59" s="90" t="s">
+      <c r="D59" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="D59" s="37" t="s">
-        <v>99</v>
-      </c>
       <c r="E59" s="37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H59" s="37"/>
       <c r="I59" s="34"/>
     </row>
     <row r="60" spans="1:47" s="40" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A60" s="58" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B60" s="67"/>
       <c r="C60" s="91" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D60" s="39"/>
       <c r="E60" s="39"/>
@@ -3205,22 +3220,22 @@
     <row r="61" spans="1:47" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="59"/>
       <c r="B61" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="C61" s="92" t="s">
         <v>102</v>
       </c>
-      <c r="C61" s="92" t="s">
-        <v>103</v>
-      </c>
       <c r="D61" s="80" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E61" s="41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F61" s="41" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G61" s="41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H61" s="41"/>
       <c r="I61" s="42"/>
@@ -3228,18 +3243,18 @@
     <row r="62" spans="1:47" s="43" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A62" s="59"/>
       <c r="B62" s="76" t="s">
+        <v>103</v>
+      </c>
+      <c r="C62" s="92" t="s">
         <v>104</v>
-      </c>
-      <c r="C62" s="92" t="s">
-        <v>105</v>
       </c>
       <c r="D62" s="80"/>
       <c r="E62" s="41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F62" s="41"/>
       <c r="G62" s="41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H62" s="41"/>
       <c r="I62" s="42"/>
@@ -3247,22 +3262,22 @@
     <row r="63" spans="1:47" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="59"/>
       <c r="B63" s="76" t="s">
+        <v>105</v>
+      </c>
+      <c r="C63" s="92" t="s">
         <v>106</v>
       </c>
-      <c r="C63" s="92" t="s">
-        <v>107</v>
-      </c>
       <c r="D63" s="80" t="s">
+        <v>237</v>
+      </c>
+      <c r="E63" s="80" t="s">
+        <v>237</v>
+      </c>
+      <c r="F63" s="80" t="s">
+        <v>237</v>
+      </c>
+      <c r="G63" s="80" t="s">
         <v>238</v>
-      </c>
-      <c r="E63" s="80" t="s">
-        <v>238</v>
-      </c>
-      <c r="F63" s="80" t="s">
-        <v>238</v>
-      </c>
-      <c r="G63" s="80" t="s">
-        <v>239</v>
       </c>
       <c r="H63" s="80"/>
       <c r="I63" s="59"/>
@@ -3270,22 +3285,22 @@
     <row r="64" spans="1:47" s="44" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A64" s="59"/>
       <c r="B64" s="76" t="s">
+        <v>107</v>
+      </c>
+      <c r="C64" s="92" t="s">
         <v>108</v>
       </c>
-      <c r="C64" s="92" t="s">
-        <v>109</v>
-      </c>
       <c r="D64" s="80" t="s">
+        <v>239</v>
+      </c>
+      <c r="E64" s="80" t="s">
+        <v>239</v>
+      </c>
+      <c r="F64" s="80" t="s">
+        <v>239</v>
+      </c>
+      <c r="G64" s="80" t="s">
         <v>240</v>
-      </c>
-      <c r="E64" s="80" t="s">
-        <v>240</v>
-      </c>
-      <c r="F64" s="80" t="s">
-        <v>240</v>
-      </c>
-      <c r="G64" s="80" t="s">
-        <v>241</v>
       </c>
       <c r="H64" s="80"/>
       <c r="I64" s="59"/>
@@ -3331,20 +3346,20 @@
     <row r="65" spans="1:47" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="59"/>
       <c r="B65" s="76" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C65" s="92"/>
       <c r="D65" s="80" t="s">
+        <v>241</v>
+      </c>
+      <c r="E65" s="80" t="s">
+        <v>241</v>
+      </c>
+      <c r="F65" s="80" t="s">
+        <v>277</v>
+      </c>
+      <c r="G65" s="80" t="s">
         <v>242</v>
-      </c>
-      <c r="E65" s="80" t="s">
-        <v>242</v>
-      </c>
-      <c r="F65" s="80" t="s">
-        <v>278</v>
-      </c>
-      <c r="G65" s="80" t="s">
-        <v>243</v>
       </c>
       <c r="H65" s="80"/>
       <c r="I65" s="59"/>
@@ -3390,20 +3405,20 @@
     <row r="66" spans="1:47" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="59"/>
       <c r="B66" s="76" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C66" s="92"/>
       <c r="D66" s="80" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E66" s="80" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F66" s="80" t="s">
+        <v>205</v>
+      </c>
+      <c r="G66" s="80" t="s">
         <v>206</v>
-      </c>
-      <c r="G66" s="80" t="s">
-        <v>207</v>
       </c>
       <c r="H66" s="80"/>
       <c r="I66" s="59"/>
@@ -3449,20 +3464,20 @@
     <row r="67" spans="1:47" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="59"/>
       <c r="B67" s="76" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C67" s="92"/>
       <c r="D67" s="80" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E67" s="80" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F67" s="80" t="s">
+        <v>208</v>
+      </c>
+      <c r="G67" s="80" t="s">
         <v>209</v>
-      </c>
-      <c r="G67" s="80" t="s">
-        <v>210</v>
       </c>
       <c r="H67" s="80"/>
       <c r="I67" s="59"/>
@@ -3508,7 +3523,7 @@
     <row r="68" spans="1:47" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="59"/>
       <c r="B68" s="76" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C68" s="92"/>
       <c r="D68" s="80">
@@ -3566,7 +3581,7 @@
     </row>
     <row r="69" spans="1:47" s="106" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="102" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B69" s="103"/>
       <c r="C69" s="104"/>
@@ -3580,22 +3595,22 @@
     <row r="70" spans="1:47" s="47" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A70" s="60"/>
       <c r="B70" s="77" t="s">
+        <v>113</v>
+      </c>
+      <c r="C70" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="C70" s="93" t="s">
-        <v>115</v>
-      </c>
       <c r="D70" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E70" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F70" s="45" t="s">
+        <v>275</v>
+      </c>
+      <c r="G70" s="45" t="s">
         <v>276</v>
-      </c>
-      <c r="G70" s="45" t="s">
-        <v>277</v>
       </c>
       <c r="H70" s="45"/>
       <c r="I70" s="46"/>
@@ -3603,20 +3618,20 @@
     <row r="71" spans="1:47" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="60"/>
       <c r="B71" s="77" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C71" s="93"/>
       <c r="D71" s="108" t="s">
+        <v>241</v>
+      </c>
+      <c r="E71" s="108" t="s">
+        <v>241</v>
+      </c>
+      <c r="F71" s="108" t="s">
+        <v>241</v>
+      </c>
+      <c r="G71" s="108" t="s">
         <v>242</v>
-      </c>
-      <c r="E71" s="108" t="s">
-        <v>242</v>
-      </c>
-      <c r="F71" s="108" t="s">
-        <v>242</v>
-      </c>
-      <c r="G71" s="108" t="s">
-        <v>243</v>
       </c>
       <c r="H71" s="45"/>
       <c r="I71" s="46"/>
@@ -3624,20 +3639,20 @@
     <row r="72" spans="1:47" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="60"/>
       <c r="B72" s="77" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C72" s="93"/>
       <c r="D72" s="108" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E72" s="45" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F72" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="G72" s="45" t="s">
         <v>206</v>
-      </c>
-      <c r="G72" s="45" t="s">
-        <v>207</v>
       </c>
       <c r="H72" s="45"/>
       <c r="I72" s="46"/>
@@ -3645,20 +3660,20 @@
     <row r="73" spans="1:47" s="47" customFormat="1" ht="42" x14ac:dyDescent="0.3">
       <c r="A73" s="60"/>
       <c r="B73" s="78" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C73" s="93"/>
       <c r="D73" s="108" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E73" s="45" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F73" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="G73" s="45" t="s">
         <v>209</v>
-      </c>
-      <c r="G73" s="45" t="s">
-        <v>210</v>
       </c>
       <c r="H73" s="45"/>
       <c r="I73" s="46"/>
@@ -3666,7 +3681,7 @@
     <row r="74" spans="1:47" s="47" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A74" s="60"/>
       <c r="B74" s="78" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C74" s="93"/>
       <c r="D74" s="108">
@@ -3687,22 +3702,22 @@
     <row r="75" spans="1:47" s="47" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A75" s="60"/>
       <c r="B75" s="77" t="s">
+        <v>119</v>
+      </c>
+      <c r="C75" s="93" t="s">
         <v>120</v>
       </c>
-      <c r="C75" s="93" t="s">
-        <v>121</v>
-      </c>
       <c r="D75" s="108" t="s">
+        <v>244</v>
+      </c>
+      <c r="E75" s="45" t="s">
         <v>245</v>
       </c>
-      <c r="E75" s="45" t="s">
+      <c r="F75" s="45" t="s">
         <v>246</v>
       </c>
-      <c r="F75" s="45" t="s">
+      <c r="G75" s="45" t="s">
         <v>247</v>
-      </c>
-      <c r="G75" s="45" t="s">
-        <v>248</v>
       </c>
       <c r="H75" s="45"/>
       <c r="I75" s="46"/>
@@ -3710,22 +3725,22 @@
     <row r="76" spans="1:47" s="47" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="A76" s="60"/>
       <c r="B76" s="77" t="s">
+        <v>265</v>
+      </c>
+      <c r="C76" s="93" t="s">
         <v>266</v>
       </c>
-      <c r="C76" s="93" t="s">
-        <v>267</v>
-      </c>
       <c r="D76" s="108" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E76" s="45" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F76" s="45" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G76" s="45" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H76" s="45"/>
       <c r="I76" s="46"/>
@@ -3733,10 +3748,10 @@
     <row r="77" spans="1:47" s="47" customFormat="1" ht="39" x14ac:dyDescent="0.3">
       <c r="A77" s="60"/>
       <c r="B77" s="77" t="s">
+        <v>267</v>
+      </c>
+      <c r="C77" s="93" t="s">
         <v>268</v>
-      </c>
-      <c r="C77" s="93" t="s">
-        <v>269</v>
       </c>
       <c r="D77" s="108">
         <v>2345678901</v>
@@ -3756,10 +3771,10 @@
     <row r="78" spans="1:47" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="60"/>
       <c r="B78" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="C78" s="93" t="s">
         <v>270</v>
-      </c>
-      <c r="C78" s="93" t="s">
-        <v>271</v>
       </c>
       <c r="D78" s="129">
         <v>44492</v>
@@ -3779,22 +3794,22 @@
     <row r="79" spans="1:47" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="60"/>
       <c r="B79" s="77" t="s">
+        <v>121</v>
+      </c>
+      <c r="C79" s="93" t="s">
         <v>122</v>
       </c>
-      <c r="C79" s="93" t="s">
-        <v>123</v>
-      </c>
       <c r="D79" s="108" t="s">
+        <v>271</v>
+      </c>
+      <c r="E79" s="45" t="s">
         <v>272</v>
       </c>
-      <c r="E79" s="45" t="s">
-        <v>273</v>
-      </c>
       <c r="F79" s="45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G79" s="45" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H79" s="45"/>
       <c r="I79" s="46"/>
@@ -3918,235 +3933,235 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" t="s">
         <v>124</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" t="s">
         <v>125</v>
       </c>
-      <c r="E1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" t="s">
         <v>126</v>
       </c>
-      <c r="G1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1" t="s">
         <v>127</v>
       </c>
-      <c r="I1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>128</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>129</v>
       </c>
-      <c r="L1" t="s">
-        <v>130</v>
-      </c>
       <c r="M1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" t="s">
         <v>131</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
         <v>132</v>
       </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>133</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>134</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J2" t="s">
         <v>135</v>
       </c>
-      <c r="H2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L2" t="s">
         <v>136</v>
       </c>
-      <c r="K2" t="s">
-        <v>92</v>
-      </c>
-      <c r="L2" t="s">
-        <v>137</v>
-      </c>
       <c r="M2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
         <v>138</v>
       </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" t="s">
         <v>139</v>
       </c>
-      <c r="D3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" t="s">
         <v>140</v>
       </c>
-      <c r="H3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>141</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>142</v>
       </c>
-      <c r="L3" t="s">
-        <v>143</v>
-      </c>
       <c r="M3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" t="s">
         <v>144</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>145</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>146</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>147</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G4" t="s">
         <v>148</v>
       </c>
-      <c r="F4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I4" t="s">
         <v>149</v>
       </c>
-      <c r="H4" t="s">
-        <v>145</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>150</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>151</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>152</v>
       </c>
-      <c r="L4" t="s">
-        <v>153</v>
-      </c>
       <c r="M4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" t="s">
         <v>154</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" t="s">
         <v>155</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5" t="s">
+        <v>144</v>
+      </c>
+      <c r="J5" t="s">
+        <v>98</v>
+      </c>
+      <c r="L5" t="s">
+        <v>156</v>
+      </c>
+      <c r="M5" t="s">
         <v>145</v>
-      </c>
-      <c r="D5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F5" t="s">
-        <v>81</v>
-      </c>
-      <c r="H5" t="s">
-        <v>81</v>
-      </c>
-      <c r="I5" t="s">
-        <v>145</v>
-      </c>
-      <c r="J5" t="s">
-        <v>99</v>
-      </c>
-      <c r="L5" t="s">
-        <v>157</v>
-      </c>
-      <c r="M5" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
+        <v>157</v>
+      </c>
+      <c r="I6" t="s">
         <v>158</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>159</v>
       </c>
-      <c r="J6" t="s">
+      <c r="L6" t="s">
         <v>160</v>
-      </c>
-      <c r="L6" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E7" t="s">
+        <v>161</v>
+      </c>
+      <c r="J7" t="s">
         <v>162</v>
       </c>
-      <c r="J7" t="s">
-        <v>163</v>
-      </c>
       <c r="L7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -4355,29 +4370,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">YVWEJ5DVYS2U-421999773-68</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">
-      <Url>https://cdcpartners.sharepoint.com/sites/NCHS/nvssmodcop/_layouts/15/DocIdRedir.aspx?ID=YVWEJ5DVYS2U-421999773-68</Url>
-      <Description>YVWEJ5DVYS2U-421999773-68</Description>
-    </_dlc_DocIdUrl>
-    <ShareFileCreator xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
-    <ShareFileCreated xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -4427,6 +4419,29 @@
 </spe:Receivers>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">YVWEJ5DVYS2U-421999773-68</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="b541edd5-2552-480e-ada6-0e2c8d317108">
+      <Url>https://cdcpartners.sharepoint.com/sites/NCHS/nvssmodcop/_layouts/15/DocIdRedir.aspx?ID=YVWEJ5DVYS2U-421999773-68</Url>
+      <Description>YVWEJ5DVYS2U-421999773-68</Description>
+    </_dlc_DocIdUrl>
+    <ShareFileCreator xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
+    <ShareFileCreated xmlns="780ae317-08c5-4e10-af93-dd385a8384a9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0980278E-2A79-4F44-8623-FE545C304BE1}">
   <ds:schemaRefs>
@@ -4448,6 +4463,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0D7A6D-D78F-4048-9348-0B4289842B11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E3EF86-6C9E-4C22-A476-13DA012C68C5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -4463,20 +4494,4 @@
     <ds:schemaRef ds:uri="b541edd5-2552-480e-ada6-0e2c8d317108"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448710E8-BE9E-4C9E-A40A-0AC1DAE48E99}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0D7A6D-D78F-4048-9348-0B4289842B11}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>